--- a/05_xlsx_docx_pdf/distritos-ejemplo.xlsx
+++ b/05_xlsx_docx_pdf/distritos-ejemplo.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFBAC970-35A5-4660-A8A3-4F8EE28809A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650"/>
+    <workbookView xWindow="52695" yWindow="3045" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distrito_población" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>DISTRITO</t>
   </si>
@@ -40,12 +41,15 @@
   </si>
   <si>
     <t>Latina</t>
+  </si>
+  <si>
+    <t>Otra</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -356,11 +360,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -412,6 +416,14 @@
         <v>233808</v>
       </c>
     </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
